--- a/5/search/FY3_Missile2_results/fine_tuned/original_top5_solutions.xlsx
+++ b/5/search/FY3_Missile2_results/fine_tuned/original_top5_solutions.xlsx
@@ -487,37 +487,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99</v>
+        <v>90</v>
       </c>
       <c r="B2" t="n">
-        <v>117.6</v>
+        <v>126</v>
       </c>
       <c r="C2" t="n">
         <v>24</v>
       </c>
       <c r="D2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>5558.479365870453</v>
+        <v>6000</v>
       </c>
       <c r="F2" t="n">
-        <v>-212.3484275042833</v>
+        <v>24</v>
       </c>
       <c r="G2" t="n">
         <v>700</v>
       </c>
       <c r="H2" t="n">
-        <v>5484.892593515528</v>
+        <v>6000</v>
       </c>
       <c r="I2" t="n">
-        <v>252.2601679116694</v>
+        <v>276</v>
       </c>
       <c r="J2" t="n">
-        <v>621.6</v>
+        <v>680.4</v>
       </c>
       <c r="K2" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -525,19 +525,19 @@
         <v>90</v>
       </c>
       <c r="B3" t="n">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="C3" t="n">
         <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E3" t="n">
         <v>6000</v>
       </c>
       <c r="F3" t="n">
-        <v>24</v>
+        <v>120</v>
       </c>
       <c r="G3" t="n">
         <v>700</v>
@@ -546,118 +546,118 @@
         <v>6000</v>
       </c>
       <c r="I3" t="n">
-        <v>276</v>
+        <v>250</v>
       </c>
       <c r="J3" t="n">
-        <v>680.4</v>
+        <v>695.1</v>
       </c>
       <c r="K3" t="n">
-        <v>2.400000000000002</v>
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="B4" t="n">
-        <v>114.8</v>
+        <v>118</v>
       </c>
       <c r="C4" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>6000</v>
+        <v>5556.977595006067</v>
       </c>
       <c r="F4" t="n">
-        <v>214.4000000000001</v>
+        <v>-202.8666194345697</v>
       </c>
       <c r="G4" t="n">
         <v>700</v>
       </c>
       <c r="H4" t="n">
-        <v>6000</v>
+        <v>5483.140527507077</v>
       </c>
       <c r="I4" t="n">
-        <v>214.4000000000001</v>
+        <v>263.3222773263354</v>
       </c>
       <c r="J4" t="n">
-        <v>700</v>
+        <v>621.6</v>
       </c>
       <c r="K4" t="n">
-        <v>2.200000000000003</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>90</v>
+        <v>99</v>
       </c>
       <c r="B5" t="n">
-        <v>95.2</v>
+        <v>138</v>
       </c>
       <c r="C5" t="n">
-        <v>32</v>
+        <v>20</v>
       </c>
       <c r="D5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="E5" t="n">
-        <v>6000</v>
+        <v>5568.240876488963</v>
       </c>
       <c r="F5" t="n">
-        <v>46.40000000000009</v>
+        <v>-273.9801799574198</v>
       </c>
       <c r="G5" t="n">
         <v>700</v>
       </c>
       <c r="H5" t="n">
-        <v>6000</v>
+        <v>5481.889051786756</v>
       </c>
       <c r="I5" t="n">
-        <v>236.8000000000001</v>
+        <v>271.2237840510963</v>
       </c>
       <c r="J5" t="n">
-        <v>680.4</v>
+        <v>621.6</v>
       </c>
       <c r="K5" t="n">
-        <v>2.100000000000001</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>99</v>
+        <v>121.5</v>
       </c>
       <c r="B6" t="n">
-        <v>120.4</v>
+        <v>108</v>
       </c>
       <c r="C6" t="n">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="D6" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="E6" t="n">
-        <v>5547.966969819749</v>
+        <v>4419.964340298971</v>
       </c>
       <c r="F6" t="n">
-        <v>-145.9757710162899</v>
+        <v>-421.6161429932249</v>
       </c>
       <c r="G6" t="n">
         <v>700</v>
       </c>
       <c r="H6" t="n">
-        <v>5491.462841047217</v>
+        <v>4024.955425373714</v>
       </c>
       <c r="I6" t="n">
-        <v>210.7772576066739</v>
+        <v>222.9798212584689</v>
       </c>
       <c r="J6" t="n">
-        <v>655.9</v>
+        <v>459.9</v>
       </c>
       <c r="K6" t="n">
-        <v>1.899999999999999</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
